--- a/01_Trunk/Figures/S01_QC/c_data/s01_qc.xlsx
+++ b/01_Trunk/Figures/S01_QC/c_data/s01_qc.xlsx
@@ -12017,7 +12017,7 @@
     <t>01_Trunk/01_Protein_Filtering/c_data/protein_filtering.xlsx</t>
   </si>
   <si>
-    <t>0cfc12775d4f74fe980b69798dcbba4a</t>
+    <t>36e4851076be5936c6ea1094c0e9b8a0</t>
   </si>
   <si>
     <t>normalize</t>
@@ -12026,7 +12026,7 @@
     <t>01_Trunk/02_Normalisation/c_data/normalisation.xlsx</t>
   </si>
   <si>
-    <t>ba0f4a175dbbad45139e7a4672b9d08f</t>
+    <t>661b5b8fd32af563512193b5db7c04c3</t>
   </si>
   <si>
     <t>quantify</t>
@@ -12035,7 +12035,7 @@
     <t>01_Trunk/03_Quantification/c_data/quantification.xlsx</t>
   </si>
   <si>
-    <t>ac8d95592cccb84fb515aaf213917d25</t>
+    <t>9e6ea46d26a72e4ac1120f2fdf0afb0e</t>
   </si>
   <si>
     <t>contrasts</t>
@@ -12044,7 +12044,7 @@
     <t>02_HRvLR_groups/02_Protein_Contrasts/c_data/protein_contrasts.xlsx</t>
   </si>
   <si>
-    <t>a427c97768bcc7bf80a6526cbc8225f6</t>
+    <t>f3294b7f02df2c8ee462be5604fcd0a5</t>
   </si>
   <si>
     <t>BiocGenerics</t>
